--- a/Testdaten/Testdaten von und für GPT-4o/OpenCart-Testfälle GPT-4o_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4o/OpenCart-Testfälle GPT-4o_ausgewertet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4o\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0D8FFC-38F0-4064-B6F5-D9FFD65CC852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6966BB80-FF24-4594-BBE8-EB7FC6AF18C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,22 +22,8 @@
     <sheet name="My Account" sheetId="12" r:id="rId7"/>
     <sheet name="My Account Information" sheetId="13" r:id="rId8"/>
     <sheet name="Change Password" sheetId="14" r:id="rId9"/>
-    <sheet name="Address Book" sheetId="15" r:id="rId10"/>
-    <sheet name="Order History" sheetId="16" r:id="rId11"/>
-    <sheet name="Order Information" sheetId="17" r:id="rId12"/>
-    <sheet name="Product Returns" sheetId="18" r:id="rId13"/>
-    <sheet name="Downloads" sheetId="19" r:id="rId14"/>
-    <sheet name="Reward Points" sheetId="20" r:id="rId15"/>
-    <sheet name="Returns" sheetId="21" r:id="rId16"/>
-    <sheet name="Transactions" sheetId="22" r:id="rId17"/>
-    <sheet name="Recurring Payments" sheetId="23" r:id="rId18"/>
-    <sheet name="Affiliate" sheetId="24" r:id="rId19"/>
-    <sheet name="Newsletter" sheetId="25" r:id="rId20"/>
-    <sheet name="Contact Us" sheetId="26" r:id="rId21"/>
-    <sheet name="Gift Certificate" sheetId="27" r:id="rId22"/>
-    <sheet name="Specail Offers" sheetId="28" r:id="rId23"/>
-    <sheet name="Header Menu Footer Options" sheetId="29" r:id="rId24"/>
-    <sheet name="Currencies" sheetId="31" r:id="rId25"/>
+    <sheet name="Order History" sheetId="16" r:id="rId10"/>
+    <sheet name="Currencies" sheetId="31" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,52 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="523">
-  <si>
-    <t>Validate the My Account functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Account &gt; Account Information functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Account &gt; 'Change Password' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Account &gt; 'Address Book' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Order History' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Order Information' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Product Returns' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Downloads' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Reward Points' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Returned Requests' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Your Transactions' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Recurring Payments' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of 'Affiliate' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of 'Newsletter' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of 'Contact Us' page functionality</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="574">
   <si>
     <t>Number of Test Cases</t>
   </si>
@@ -1896,6 +1837,229 @@
   <si>
     <t>(7/13)*100
 = 53,8%</t>
+  </si>
+  <si>
+    <t>TC_OH_001</t>
+  </si>
+  <si>
+    <t>Access Order History page</t>
+  </si>
+  <si>
+    <t>Verify user can access the Order History page</t>
+  </si>
+  <si>
+    <t>1. Navigate to OpenCart.
+2. Log in with valid credentials.
+3. Click on 'Purchases' in the sidebar.
+4. Click on 'Your Orders'.</t>
+  </si>
+  <si>
+    <t>The Order History page is displayed successfully.</t>
+  </si>
+  <si>
+    <t>TC_OH_002</t>
+  </si>
+  <si>
+    <t>No previous orders</t>
+  </si>
+  <si>
+    <t>Open OpenCart
+User is logged in
+User has no past orders</t>
+  </si>
+  <si>
+    <t>Verify empty order history</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Check if any orders are listed.</t>
+  </si>
+  <si>
+    <t>The system displays 'No results!' if there are no past orders.</t>
+  </si>
+  <si>
+    <t>TC_OH_003</t>
+  </si>
+  <si>
+    <t>Existing orders are displayed</t>
+  </si>
+  <si>
+    <t>Open OpenCart
+User is logged in
+User has past orders</t>
+  </si>
+  <si>
+    <t>Verify order details are shown</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Check if past orders are listed with correct details (ID, Extension Name, Amount, Status, Add Date, Action).</t>
+  </si>
+  <si>
+    <t>All past orders should be displayed correctly with the following details: ID, Extension Name, Amount, Status, Add Date, Action.</t>
+  </si>
+  <si>
+    <t>TC_OH_004</t>
+  </si>
+  <si>
+    <t>Filter orders by date</t>
+  </si>
+  <si>
+    <t>Verify filtering functionality</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Apply a date filter (if available).
+3. Check if only orders within the selected range are displayed.</t>
+  </si>
+  <si>
+    <t>The system correctly filters and displays orders within the selected date range.</t>
+  </si>
+  <si>
+    <t>TC_OH_005</t>
+  </si>
+  <si>
+    <t>Click on an order</t>
+  </si>
+  <si>
+    <t>Verify user can view order details</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Click on an order ID or 'Action' button.</t>
+  </si>
+  <si>
+    <t>The system navigates to the order details page.</t>
+  </si>
+  <si>
+    <t>TC_OH_006</t>
+  </si>
+  <si>
+    <t>Slow loading orders</t>
+  </si>
+  <si>
+    <t>Open OpenCart
+User is logged in
+User has many past orders</t>
+  </si>
+  <si>
+    <t>Verify performance with many orders</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Observe loading time when multiple orders are displayed.</t>
+  </si>
+  <si>
+    <t>The system loads all orders within an acceptable time without errors.</t>
+  </si>
+  <si>
+    <t>TC_OH_007</t>
+  </si>
+  <si>
+    <t>Unauthorized access to orders</t>
+  </si>
+  <si>
+    <t>Open OpenCart
+User is NOT logged in</t>
+  </si>
+  <si>
+    <t>Verify unauthorized users cannot access order history</t>
+  </si>
+  <si>
+    <t>1. Open OpenCart without logging in.
+2. Try to access 'Your Orders' page directly via URL.</t>
+  </si>
+  <si>
+    <t>The system redirects to the login page or displays an authorization error.</t>
+  </si>
+  <si>
+    <t>TC_OH_008</t>
+  </si>
+  <si>
+    <t>Logout from Order History page</t>
+  </si>
+  <si>
+    <t>Verify user can log out from Order History</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Click on 'Logout' button.</t>
+  </si>
+  <si>
+    <t>The user is logged out and redirected to the homepage or login page.</t>
+  </si>
+  <si>
+    <t>TC_OH_009</t>
+  </si>
+  <si>
+    <t>Order History page layout on different browsers</t>
+  </si>
+  <si>
+    <t>Verify the Order History page renders correctly across different browsers</t>
+  </si>
+  <si>
+    <t>1. Open OpenCart in different browsers (Chrome, Firefox, Edge, Safari).
+2. Navigate to 'Your Orders' page.
+3. Verify that all elements (order list, filters, buttons) are displayed correctly.</t>
+  </si>
+  <si>
+    <t>The Order History page should render correctly across all tested browsers with no UI distortions.</t>
+  </si>
+  <si>
+    <t>TC_OH_010</t>
+  </si>
+  <si>
+    <t>Order History page responsiveness</t>
+  </si>
+  <si>
+    <t>Verify the page adjusts correctly on different screen sizes</t>
+  </si>
+  <si>
+    <t>1. Open OpenCart on different devices (PC, tablet, mobile).
+2. Navigate to 'Your Orders' page.
+3. Resize the browser window to different resolutions.
+4. Verify that the page elements adjust properly without overlapping or breaking.</t>
+  </si>
+  <si>
+    <t>The Order History page should be fully responsive and adapt to different screen sizes without layout issues.</t>
+  </si>
+  <si>
+    <t>TC_OH_011</t>
+  </si>
+  <si>
+    <t>Button and link functionality on Order History page</t>
+  </si>
+  <si>
+    <t>Verify all buttons and links function correctly</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Click on each button and link (e.g., 'Action', 'Back', 'Logout').
+3. Verify that each action performs the expected functionality.</t>
+  </si>
+  <si>
+    <t>All buttons and links should function correctly and navigate to the expected pages without errors.</t>
+  </si>
+  <si>
+    <t>Halluzination, es gibt keine Filter Funktion in den Screenshots</t>
+  </si>
+  <si>
+    <t>Halluzination, keine Informationen dazu</t>
+  </si>
+  <si>
+    <t>Nur halb richtig! Der User kommt auf die Hompage auf welcher er auf Login klicken kann, aber er kommt nicht direkt auf die Login Page</t>
+  </si>
+  <si>
+    <t>My Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Account Information </t>
+  </si>
+  <si>
+    <t>Change Password</t>
+  </si>
+  <si>
+    <t>Order History</t>
   </si>
 </sst>
 </file>
@@ -1945,24 +2109,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -2000,12 +2151,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2044,13 +2195,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2096,8 +2244,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7F2BEDD-E806-43D3-8505-12EAAAE9CC42}" name="Tabelle1" displayName="Tabelle1" ref="A1:B22" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="A1:B22" xr:uid="{E7F2BEDD-E806-43D3-8505-12EAAAE9CC42}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7F2BEDD-E806-43D3-8505-12EAAAE9CC42}" name="Tabelle1" displayName="Tabelle1" ref="A1:B11" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="A1:B11" xr:uid="{E7F2BEDD-E806-43D3-8505-12EAAAE9CC42}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{864D606B-93C4-4F0A-8037-1114AF469597}" name="Test Szenario auf Open Cart" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{201C25FB-195B-4F56-8A72-5E70DDDF2E9B}" name="Number of Test Cases" dataDxfId="0"/>
@@ -2369,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D094905A-5468-4F97-B712-0809D4979503}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.5703125" customWidth="1"/>
@@ -2378,15 +2526,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="B2" s="5">
         <v>20</v>
@@ -2394,7 +2542,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="B3" s="5">
         <v>22</v>
@@ -2402,7 +2550,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B4" s="5">
         <v>10</v>
@@ -2410,7 +2558,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="B5" s="5">
         <v>22</v>
@@ -2418,113 +2566,49 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="B6" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="B7" s="5">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>1</v>
+        <v>571</v>
       </c>
       <c r="B8" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>2</v>
+        <v>572</v>
       </c>
       <c r="B9" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="5"/>
-    </row>
-    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="5"/>
-    </row>
-    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="5"/>
-    </row>
-    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="5"/>
-    </row>
-    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="5"/>
-    </row>
-    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="5"/>
-    </row>
-    <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="5"/>
-    </row>
-    <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="5"/>
-    </row>
-    <row r="18" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="B10" s="5">
         <v>11</v>
       </c>
-      <c r="B18" s="5"/>
-    </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="5"/>
-    </row>
-    <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="5"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="B22" s="5">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="B11" s="5">
         <v>3</v>
       </c>
     </row>
@@ -2537,91 +2621,578 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884EF907-734D-47C2-A462-0A7DDD7773AA}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E5B671-0B83-466E-B4C9-A5B4C2F32FB0}">
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" customWidth="1"/>
+    <col min="6" max="6" width="21.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="180" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I13" s="5">
+        <f>SUM(I2:I12)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E5B671-0B83-466E-B4C9-A5B4C2F32FB0}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7665E2E6-5E9A-4EF8-B9F5-D0AC7746DA1E}">
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAF1EEB-08B3-4462-A935-285A740C21B1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB318571-7AA6-48E7-8B34-1554E4D4D71F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6366D9F1-B0C3-4E0E-A154-D57D8B3B5093}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD04566-2B9F-4B07-AA34-BF57464EB60D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E879D26-DF42-416A-B355-648FF3505B03}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2166216-EEEF-4E1B-B517-FAF39C77E32F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3BDDD2-D55F-46D4-BF02-5AC4E8168912}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51240DEB-4720-4744-A3E5-ABE3B15218B8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H5" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I5" s="5">
+        <f>SUM(I2:I4)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H6" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="H7" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2644,57 +3215,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -2702,28 +3273,28 @@
     </row>
     <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="I3" s="7">
         <v>0</v>
@@ -2731,28 +3302,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -2760,28 +3331,28 @@
     </row>
     <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -2789,28 +3360,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -2818,28 +3389,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -2847,28 +3418,28 @@
     </row>
     <row r="8" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="I8" s="7">
         <v>0</v>
@@ -2876,28 +3447,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -2905,28 +3476,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -2934,28 +3505,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -2963,28 +3534,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
@@ -2992,28 +3563,28 @@
     </row>
     <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
@@ -3021,28 +3592,28 @@
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
@@ -3050,28 +3621,28 @@
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -3079,28 +3650,28 @@
     </row>
     <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
@@ -3108,28 +3679,28 @@
     </row>
     <row r="17" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="I17" s="4">
         <v>1</v>
@@ -3137,28 +3708,28 @@
     </row>
     <row r="18" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I18" s="4">
         <v>1</v>
@@ -3166,28 +3737,28 @@
     </row>
     <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
@@ -3195,28 +3766,28 @@
     </row>
     <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -3224,28 +3795,28 @@
     </row>
     <row r="21" spans="1:9" ht="195" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="I21" s="7">
         <v>0</v>
@@ -3253,7 +3824,7 @@
     </row>
     <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H22" s="6" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I22" s="5">
         <f>SUM(I2:I21)</f>
@@ -3262,7 +3833,7 @@
     </row>
     <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H23" s="6" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I23" s="3">
         <v>27</v>
@@ -3270,217 +3841,10 @@
     </row>
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F321C8C-3303-4D7C-9741-9B98D2CB30B9}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D0881DA-FFFD-4EA2-A7CE-6EEFF29BDA2D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C6C93B5-A0D8-4D55-82E6-2C662B74A26E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A08BA0-82AB-40C6-AB10-9C065EBEE794}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC3A216-5155-4CEF-8A20-6800539D6F36}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7665E2E6-5E9A-4EF8-B9F5-D0AC7746DA1E}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="I2" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="I3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="I4" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="H5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="I5" s="5">
-        <f>SUM(I2:I4)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="H6" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I6" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="H7" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>373</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -3505,57 +3869,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -3563,28 +3927,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -3592,28 +3956,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -3621,28 +3985,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -3650,28 +4014,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -3679,28 +4043,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -3708,28 +4072,28 @@
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
@@ -3737,28 +4101,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -3766,28 +4130,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -3795,28 +4159,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -3824,28 +4188,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
@@ -3853,28 +4217,28 @@
     </row>
     <row r="13" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="I13" s="7">
         <v>0</v>
@@ -3882,28 +4246,28 @@
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="I14" s="7">
         <v>0</v>
@@ -3911,28 +4275,28 @@
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -3940,28 +4304,28 @@
     </row>
     <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
@@ -3969,28 +4333,28 @@
     </row>
     <row r="17" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="I17" s="7">
         <v>0</v>
@@ -3998,28 +4362,28 @@
     </row>
     <row r="18" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="I18" s="7">
         <v>0</v>
@@ -4027,28 +4391,28 @@
     </row>
     <row r="19" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>197</v>
-      </c>
       <c r="G19" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="I19" s="7">
         <v>0</v>
@@ -4056,28 +4420,28 @@
     </row>
     <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -4085,28 +4449,28 @@
     </row>
     <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I21" s="4">
         <v>1</v>
@@ -4114,28 +4478,28 @@
     </row>
     <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I22" s="4">
         <v>1</v>
@@ -4143,28 +4507,28 @@
     </row>
     <row r="23" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="I23" s="4">
         <v>1</v>
@@ -4173,7 +4537,7 @@
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G24" s="6"/>
       <c r="H24" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I24" s="3">
         <f>SUM(I2:I23)</f>
@@ -4183,7 +4547,7 @@
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G25" s="6"/>
       <c r="H25" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I25" s="3">
         <v>23</v>
@@ -4192,10 +4556,10 @@
     <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G26" s="6"/>
       <c r="H26" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -4221,57 +4585,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -4279,28 +4643,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="I3" s="12">
         <v>0</v>
@@ -4308,28 +4672,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -4337,28 +4701,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -4366,28 +4730,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>225</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -4395,28 +4759,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -4424,28 +4788,28 @@
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
@@ -4453,28 +4817,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -4482,28 +4846,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -4511,28 +4875,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -4541,7 +4905,7 @@
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I12" s="3">
         <f>SUM(I2:I11)</f>
@@ -4550,7 +4914,7 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H13" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I13" s="3">
         <v>11</v>
@@ -4558,10 +4922,10 @@
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H14" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -4587,57 +4951,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -4645,28 +5009,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -4674,28 +5038,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -4703,28 +5067,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -4732,28 +5096,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -4761,28 +5125,28 @@
     </row>
     <row r="7" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -4790,28 +5154,28 @@
     </row>
     <row r="8" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
@@ -4819,28 +5183,28 @@
     </row>
     <row r="9" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="I9" s="7">
         <v>0</v>
@@ -4848,28 +5212,28 @@
     </row>
     <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -4877,28 +5241,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -4906,28 +5270,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
@@ -4935,28 +5299,28 @@
     </row>
     <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
@@ -4964,28 +5328,28 @@
     </row>
     <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
@@ -4993,28 +5357,28 @@
     </row>
     <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -5022,28 +5386,28 @@
     </row>
     <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
@@ -5051,28 +5415,28 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="I17" s="7">
         <v>0</v>
@@ -5080,28 +5444,28 @@
     </row>
     <row r="18" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I18" s="4">
         <v>1</v>
@@ -5109,28 +5473,28 @@
     </row>
     <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
@@ -5138,28 +5502,28 @@
     </row>
     <row r="20" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -5167,28 +5531,28 @@
     </row>
     <row r="21" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="I21" s="7">
         <v>0</v>
@@ -5196,28 +5560,28 @@
     </row>
     <row r="22" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="I22" s="7">
         <v>0</v>
@@ -5225,28 +5589,28 @@
     </row>
     <row r="23" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="I23" s="7">
         <v>0</v>
@@ -5254,7 +5618,7 @@
     </row>
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H24" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I24" s="3">
         <f>SUM(I2:I23)</f>
@@ -5263,7 +5627,7 @@
     </row>
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H25" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I25" s="3">
         <v>25</v>
@@ -5271,10 +5635,10 @@
     </row>
     <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H26" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -5299,57 +5663,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -5357,28 +5721,28 @@
     </row>
     <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I3" s="14">
         <v>1</v>
@@ -5386,28 +5750,28 @@
     </row>
     <row r="4" spans="1:9" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="I4" s="14">
         <v>1</v>
@@ -5415,28 +5779,28 @@
     </row>
     <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>342</v>
-      </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I5" s="14">
         <v>1</v>
@@ -5444,28 +5808,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I6" s="14">
         <v>1</v>
@@ -5473,28 +5837,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I7" s="14">
         <v>1</v>
@@ -5502,28 +5866,28 @@
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I8" s="14">
         <v>1</v>
@@ -5531,28 +5895,28 @@
     </row>
     <row r="9" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="I9" s="12">
         <v>0</v>
@@ -5560,28 +5924,28 @@
     </row>
     <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I10" s="14">
         <v>1</v>
@@ -5590,7 +5954,7 @@
     <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G11" s="5"/>
       <c r="H11" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I11" s="5">
         <f>SUM(I2:I10)</f>
@@ -5600,7 +5964,7 @@
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G12" s="5"/>
       <c r="H12" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I12" s="5">
         <v>9</v>
@@ -5609,10 +5973,10 @@
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G13" s="5"/>
       <c r="H13" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -5637,57 +6001,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -5695,28 +6059,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -5724,28 +6088,28 @@
     </row>
     <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -5753,28 +6117,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="I5" s="7">
         <v>0</v>
@@ -5782,28 +6146,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -5811,28 +6175,28 @@
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="I7" s="7">
         <v>0</v>
@@ -5840,28 +6204,28 @@
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="I8" s="7">
         <v>0</v>
@@ -5869,28 +6233,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="F9" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>451</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>466</v>
       </c>
       <c r="I9" s="7">
         <v>0</v>
@@ -5898,28 +6262,28 @@
     </row>
     <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="I10" s="7">
         <v>0</v>
@@ -5927,28 +6291,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -5956,28 +6320,28 @@
     </row>
     <row r="12" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
@@ -5985,7 +6349,7 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H13" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I13" s="5">
         <f>SUM(I2:I12)</f>
@@ -5994,7 +6358,7 @@
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H14" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I14" s="5">
         <v>10</v>
@@ -6002,10 +6366,10 @@
     </row>
     <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H15" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -6031,57 +6395,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -6089,28 +6453,28 @@
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -6118,28 +6482,28 @@
     </row>
     <row r="4" spans="1:9" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="I4" s="7">
         <v>0</v>
@@ -6147,28 +6511,28 @@
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -6176,28 +6540,28 @@
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -6205,28 +6569,28 @@
     </row>
     <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>403</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>418</v>
       </c>
       <c r="I7" s="7">
         <v>0</v>
@@ -6234,28 +6598,28 @@
     </row>
     <row r="8" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>407</v>
-      </c>
       <c r="G8" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
@@ -6263,28 +6627,28 @@
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -6292,28 +6656,28 @@
     </row>
     <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -6321,28 +6685,28 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -6350,7 +6714,7 @@
     </row>
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H12" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I12" s="3">
         <f>SUM(I2:I11)</f>
@@ -6359,7 +6723,7 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H13" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I13" s="3">
         <v>13</v>
@@ -6367,10 +6731,10 @@
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H14" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -6396,57 +6760,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="I2" s="7">
         <v>0</v>
@@ -6454,28 +6818,28 @@
     </row>
     <row r="3" spans="1:9" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -6483,28 +6847,28 @@
     </row>
     <row r="4" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -6512,28 +6876,28 @@
     </row>
     <row r="5" spans="1:9" ht="165" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -6541,28 +6905,28 @@
     </row>
     <row r="6" spans="1:9" ht="180" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -6570,28 +6934,28 @@
     </row>
     <row r="7" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="I7" s="7">
         <v>0</v>
@@ -6599,28 +6963,28 @@
     </row>
     <row r="8" spans="1:9" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="I8" s="7">
         <v>0</v>
@@ -6628,28 +6992,28 @@
     </row>
     <row r="9" spans="1:9" ht="180" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -6657,28 +7021,28 @@
     </row>
     <row r="10" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -6686,28 +7050,28 @@
     </row>
     <row r="11" spans="1:9" ht="180" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -6715,7 +7079,7 @@
     </row>
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H12" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I12" s="3">
         <f>SUM(I2:I11)</f>
@@ -6724,7 +7088,7 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H13" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I13" s="3">
         <v>13</v>
@@ -6732,10 +7096,10 @@
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H14" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>

--- a/Testdaten/Testdaten von und für GPT-4o/OpenCart-Testfälle GPT-4o_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4o/OpenCart-Testfälle GPT-4o_ausgewertet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4o\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6966BB80-FF24-4594-BBE8-EB7FC6AF18C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0322790-B4CA-43E2-B1DD-91A1B59F984B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Szenarien" sheetId="33" r:id="rId1"/>
@@ -6341,7 +6341,7 @@
         <v>15</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>

--- a/Testdaten/Testdaten von und für GPT-4o/OpenCart-Testfälle GPT-4o_ausgewertet.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4o/OpenCart-Testfälle GPT-4o_ausgewertet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4o\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0322790-B4CA-43E2-B1DD-91A1B59F984B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED3652E-043F-41BE-A1BA-45BDD1BD37D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3051,7 +3051,7 @@
     <col min="9" max="9" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
